--- a/data/unapproved_childcare_facilities/data.xlsx
+++ b/data/unapproved_childcare_facilities/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -542,125 +542,125 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="str">
-        <v>34.333181</v>
+        <v>34.339921</v>
       </c>
       <c r="C4" t="str">
-        <v>134.050484</v>
+        <v>134.052268</v>
       </c>
       <c r="D4" t="str">
-        <v>２４時間保育クラブキッズ</v>
+        <v>夜間保育カナリヤ瓦町園</v>
       </c>
       <c r="E4" t="str">
-        <v>761-0071 高松市藤塚町二丁目12-１3第2八十川ビル1F</v>
+        <v>760-0052 高松市瓦町二丁目6番地3</v>
       </c>
       <c r="F4" t="str">
-        <v>087-837-5272</v>
+        <v>087-813-2862</v>
       </c>
       <c r="G4" t="str">
-        <v>株式会社　クラブキッズ　代表取締役　中谷　伊都子</v>
+        <v>松熊　徳海</v>
       </c>
       <c r="H4" t="str">
-        <v>H12.10.15</v>
+        <v>S47.4.1</v>
       </c>
       <c r="I4" t="str">
-        <v>0：00～24：00（24時間）</v>
+        <v>16：00～1：00（1：00～2：00）</v>
       </c>
       <c r="J4" t="str">
-        <v>0：00～24：00（24時間）</v>
+        <v>16：00～1：00（1：00～2：00）</v>
       </c>
       <c r="K4" t="str">
-        <v>0：00～24：00（24時間）</v>
+        <v>13：00～21：00</v>
       </c>
       <c r="L4" t="str">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M4" t="str">
-        <v>3ヶ月～5歳児</v>
+        <v>0～5歳児</v>
       </c>
       <c r="N4" t="str">
-        <v>月極め、一時預かり、夜間保育、24時間保育</v>
+        <v>月極め、一時預かり、夜間保育</v>
       </c>
       <c r="O4" t="str">
-        <v>構造：鉄筋コンクリート造5階建ての１階（集合住宅、事務所用建物）、保育室：73.2㎡、屋外：なし</v>
+        <v>構造：鉄骨造3階建ての１階（集合住宅）、保育室：28.5㎡、屋外：なし</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="str">
-        <v>34.339921</v>
+        <v>34.31565</v>
       </c>
       <c r="C5" t="str">
-        <v>134.052268</v>
+        <v>134.083089</v>
       </c>
       <c r="D5" t="str">
-        <v>夜間保育カナリヤ瓦町園</v>
+        <v>リバティー・インターナショナルアカデミー高松校　英語バイリンガル保育園</v>
       </c>
       <c r="E5" t="str">
-        <v>760-0052 高松市瓦町二丁目6番地3</v>
+        <v>761-0311 高松市元山町689-2</v>
       </c>
       <c r="F5" t="str">
-        <v>087-813-2862</v>
+        <v>087-813-5036</v>
       </c>
       <c r="G5" t="str">
-        <v>松熊　徳海</v>
+        <v>株式会社　リバティー・インターナショナルアカデミー　代表取締役　森村　文代</v>
       </c>
       <c r="H5" t="str">
-        <v>S47.4.1</v>
+        <v>H21.4.1</v>
       </c>
       <c r="I5" t="str">
-        <v>16：00～1：00（1：00～2：00）</v>
+        <v>8：30～18：30（8：00～8：30）</v>
       </c>
       <c r="J5" t="str">
-        <v>16：00～1：00（1：00～2：00）</v>
+        <v>休</v>
       </c>
       <c r="K5" t="str">
-        <v>13：00～21：00</v>
+        <v>休</v>
       </c>
       <c r="L5" t="str">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="M5" t="str">
-        <v>0～5歳児</v>
+        <v>1～5歳児</v>
       </c>
       <c r="N5" t="str">
-        <v>月極め、一時預かり、夜間保育</v>
+        <v>月極め、一時預かり</v>
       </c>
       <c r="O5" t="str">
-        <v>構造：鉄骨造3階建ての１階（集合住宅）、保育室：28.5㎡、屋外：なし</v>
+        <v>構造：鉄筋コンクリート造2階建て（専用建物）、保育室：172.55㎡、屋外：350㎡</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="str">
-        <v>34.31565</v>
+        <v>34.299814</v>
       </c>
       <c r="C6" t="str">
-        <v>134.083089</v>
+        <v>134.041817</v>
       </c>
       <c r="D6" t="str">
-        <v>リバティー・インターナショナルアカデミー高松校　英語バイリンガル保育園</v>
+        <v>プリスクール　　イングリッシュ　ワールド</v>
       </c>
       <c r="E6" t="str">
-        <v>761-0311 高松市元山町689-2</v>
+        <v>761-8074 高松市太田上町969番地</v>
       </c>
       <c r="F6" t="str">
-        <v>087-813-5036</v>
+        <v>087-865-6254</v>
       </c>
       <c r="G6" t="str">
-        <v>株式会社　リバティー・インターナショナルアカデミー　代表取締役　森村　文代</v>
+        <v>有限会社　EW　代表取締役　東原　睦美</v>
       </c>
       <c r="H6" t="str">
-        <v>H21.4.1</v>
+        <v>H23.4.7</v>
       </c>
       <c r="I6" t="str">
-        <v>8：30～18：30（8：00～8：30）</v>
+        <v>8：30～16：00（16：00～17：00）</v>
       </c>
       <c r="J6" t="str">
         <v>休</v>
@@ -669,378 +669,378 @@
         <v>休</v>
       </c>
       <c r="L6" t="str">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="M6" t="str">
-        <v>1～5歳児</v>
+        <v>2～5歳児</v>
       </c>
       <c r="N6" t="str">
-        <v>月極め、一時預かり</v>
+        <v>月極め</v>
       </c>
       <c r="O6" t="str">
-        <v>構造：鉄筋コンクリート造2階建て（専用建物）、保育室：172.55㎡、屋外：350㎡</v>
+        <v>構造：木造2階建ての１階（業務用建物）、保育室：81.21㎡、屋外：350㎡</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="str">
-        <v>34.299814</v>
+        <v>34.333993</v>
       </c>
       <c r="C7" t="str">
-        <v>134.041817</v>
+        <v>134.073675</v>
       </c>
       <c r="D7" t="str">
-        <v>プリスクール　　イングリッシュ　ワールド</v>
+        <v>アローナック</v>
       </c>
       <c r="E7" t="str">
-        <v>761-8074 高松市太田上町969番地</v>
+        <v>760-0080 高松市木太町2344-1</v>
       </c>
       <c r="F7" t="str">
-        <v>087-865-6254</v>
+        <v>087-813-2277</v>
       </c>
       <c r="G7" t="str">
-        <v>有限会社　EW　代表取締役　東原　睦美</v>
+        <v>株式会社　エヌ．クオリティー　代表取締役　川田　直人</v>
       </c>
       <c r="H7" t="str">
-        <v>H23.4.7</v>
+        <v>H23.8.1</v>
       </c>
       <c r="I7" t="str">
-        <v>8：30～16：00（16：00～17：00）</v>
+        <v>9：00～25：00</v>
       </c>
       <c r="J7" t="str">
-        <v>休</v>
+        <v>9：00～25：00</v>
       </c>
       <c r="K7" t="str">
-        <v>休</v>
+        <v>9：00～25：00</v>
       </c>
       <c r="L7" t="str">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M7" t="str">
-        <v>2～5歳児</v>
+        <v>0～5歳児</v>
       </c>
       <c r="N7" t="str">
-        <v>月極め</v>
+        <v>月極め、一時預かり、夜間保育、24時間保育</v>
       </c>
       <c r="O7" t="str">
-        <v>構造：木造2階建ての１階（業務用建物）、保育室：81.21㎡、屋外：350㎡</v>
+        <v>構造：鉄筋コンクリート造2階建ての１階（業務用建物）、保育室：61.5㎡、屋外：なし</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="str">
-        <v>34.333993</v>
+        <v>34.317816</v>
       </c>
       <c r="C8" t="str">
-        <v>134.073675</v>
+        <v>134.051066</v>
       </c>
       <c r="D8" t="str">
-        <v>アローナック</v>
+        <v>トビウメ小児科医院付属　一時預かり保育室あすなろ</v>
       </c>
       <c r="E8" t="str">
-        <v>760-0080 高松市木太町2344-1</v>
+        <v>761-8071 高松市伏石町1352-2</v>
       </c>
       <c r="F8" t="str">
-        <v>087-813-2277</v>
+        <v>087-865-3111, 080-2972-4406</v>
       </c>
       <c r="G8" t="str">
-        <v>株式会社　エヌ．クオリティー　代表取締役　川田　直人</v>
+        <v>トビウメ小児科医院　飛梅　董</v>
       </c>
       <c r="H8" t="str">
-        <v>H23.8.1</v>
+        <v>H25.11.1</v>
       </c>
       <c r="I8" t="str">
-        <v>9：00～25：00</v>
+        <v>8：00～17：00（17：00～18：00）</v>
       </c>
       <c r="J8" t="str">
-        <v>9：00～25：00</v>
+        <v>8：00～17：00（17：00～18：00）</v>
       </c>
       <c r="K8" t="str">
-        <v>9：00～25：00</v>
+        <v>休</v>
       </c>
       <c r="L8" t="str">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M8" t="str">
-        <v>0～5歳児</v>
+        <v>3ヶ月～5歳児</v>
       </c>
       <c r="N8" t="str">
-        <v>月極め、一時預かり、夜間保育、24時間保育</v>
+        <v>月極め、一時預かり</v>
       </c>
       <c r="O8" t="str">
-        <v>構造：鉄筋コンクリート造2階建ての１階（業務用建物）、保育室：61.5㎡、屋外：なし</v>
+        <v>構造：鉄筋コンクリート造2階建ての2階（専用建物）、保育室：102㎡、屋外：500㎡</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="str">
-        <v>34.317816</v>
+        <v>34.342954</v>
       </c>
       <c r="C9" t="str">
-        <v>134.051066</v>
+        <v>134.014555</v>
       </c>
       <c r="D9" t="str">
-        <v>トビウメ小児科医院付属　一時預かり保育室あすなろ</v>
+        <v>託児所　かくれんぼ（休止中）</v>
       </c>
       <c r="E9" t="str">
-        <v>761-8071 高松市伏石町1352-2</v>
+        <v>761-8031 高松市郷東町11-13</v>
       </c>
       <c r="F9" t="str">
-        <v>087-865-3111, 080-2972-4406</v>
+        <v>087-880-8880</v>
       </c>
       <c r="G9" t="str">
-        <v>トビウメ小児科医院　飛梅　董</v>
+        <v>福本　誠</v>
       </c>
       <c r="H9" t="str">
-        <v>H25.11.1</v>
+        <v>H25.3.27</v>
       </c>
       <c r="I9" t="str">
-        <v>8：00～17：00（17：00～18：00）</v>
+        <v>ー</v>
       </c>
       <c r="J9" t="str">
-        <v>8：00～17：00（17：00～18：00）</v>
+        <v>ー</v>
       </c>
       <c r="K9" t="str">
-        <v>休</v>
+        <v>ー</v>
       </c>
       <c r="L9" t="str">
-        <v>10</v>
+        <v>ー</v>
       </c>
       <c r="M9" t="str">
-        <v>3ヶ月～5歳児</v>
+        <v>4ヶ月～2歳児</v>
       </c>
       <c r="N9" t="str">
         <v>月極め、一時預かり</v>
       </c>
       <c r="O9" t="str">
-        <v>構造：鉄筋コンクリート造2階建ての2階（専用建物）、保育室：102㎡、屋外：500㎡</v>
+        <v>構造：木造1階建て（集合住宅）、保育室：35.38㎡、屋外：なし</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="str">
-        <v>34.342954</v>
+        <v>34.249749</v>
       </c>
       <c r="C10" t="str">
-        <v>134.014555</v>
+        <v>134.009329</v>
       </c>
       <c r="D10" t="str">
-        <v>託児所　かくれんぼ（休止中）</v>
+        <v>Ｐｅｔｉｔ-Ｐｅｔｉｔｅ</v>
       </c>
       <c r="E10" t="str">
-        <v>761-8031 高松市郷東町11-13</v>
+        <v>761-1404 高松市香南町横井98-13</v>
       </c>
       <c r="F10" t="str">
-        <v>087-880-8880</v>
+        <v>087-805-5451</v>
       </c>
       <c r="G10" t="str">
-        <v>福本　誠</v>
+        <v>宮本　尚枝</v>
       </c>
       <c r="H10" t="str">
-        <v>H25.3.27</v>
+        <v>H27.8.1</v>
       </c>
       <c r="I10" t="str">
-        <v>ー</v>
+        <v>8：00～18：00（18：00～8：00）</v>
       </c>
       <c r="J10" t="str">
-        <v>ー</v>
+        <v>8：00～18：00（18：00～8：00）</v>
       </c>
       <c r="K10" t="str">
-        <v>ー</v>
+        <v>8：00～18：00（18：00～8：00）</v>
       </c>
       <c r="L10" t="str">
-        <v>ー</v>
+        <v>5</v>
       </c>
       <c r="M10" t="str">
-        <v>4ヶ月～2歳児</v>
+        <v>5ヶ月～3歳児</v>
       </c>
       <c r="N10" t="str">
-        <v>月極め、一時預かり</v>
+        <v>月極め、一時預かり、夜間保育、24時間保育</v>
       </c>
       <c r="O10" t="str">
-        <v>構造：木造1階建て（集合住宅）、保育室：35.38㎡、屋外：なし</v>
+        <v>構造：木造2階建ての1階（集合住宅）、保育室：9.9㎡、屋外：なし</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>11</v>
+      </c>
+      <c r="B11" t="str">
+        <v>34.350335</v>
+      </c>
+      <c r="C11" t="str">
+        <v>134.056131</v>
+      </c>
+      <c r="D11" t="str">
+        <v>事業所内保育所たまも（休止中）</v>
+      </c>
+      <c r="E11" t="str">
+        <v>760-0031 高松市北浜町7-10</v>
+      </c>
+      <c r="F11" t="str">
+        <v>087-811-4450</v>
+      </c>
+      <c r="G11" t="str">
+        <v>社会福祉法人さぬき　理事長　藤目　真晧</v>
+      </c>
+      <c r="H11" t="str">
+        <v>H27.1.5</v>
+      </c>
+      <c r="I11" t="str">
+        <v>ー</v>
+      </c>
+      <c r="J11" t="str">
+        <v>ー</v>
+      </c>
+      <c r="K11" t="str">
+        <v>ー</v>
+      </c>
+      <c r="L11" t="str">
+        <v>ー</v>
+      </c>
+      <c r="M11" t="str">
+        <v>3ヶ月～5歳児</v>
+      </c>
+      <c r="N11" t="str">
+        <v>月極め、一時預かり</v>
+      </c>
+      <c r="O11" t="str">
+        <v>構造：鉄筋コンクリート造6階建ての1階（老人福祉施設）、保育室：95.00㎡、屋外：なし</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>12</v>
+      </c>
+      <c r="B12" t="str">
+        <v>34.292238</v>
+      </c>
+      <c r="C12" t="str">
+        <v>134.029099</v>
+      </c>
+      <c r="D12" t="str">
+        <v>託児所 エンジェル</v>
+      </c>
+      <c r="E12" t="str">
+        <v>761-8084 高松市一宮町880番地1</v>
+      </c>
+      <c r="F12" t="str">
+        <v>087-814-3575</v>
+      </c>
+      <c r="G12" t="str">
+        <v>社会福祉法人　喜勝会　理事長　小出　克元</v>
+      </c>
+      <c r="H12" t="str">
+        <v>H24.11.1</v>
+      </c>
+      <c r="I12" t="str">
+        <v>8：30～17：30（7：30～8：30,17：30～18：30）</v>
+      </c>
+      <c r="J12" t="str">
+        <v>8：30～17：30（7：30～8：30,17：30～18：30）</v>
+      </c>
+      <c r="K12" t="str" xml:space="preserve">
+        <v xml:space="preserve">祝：8：30～17：30（7：30～8：30,17：30～18：30）
+日：休</v>
+      </c>
+      <c r="L12" t="str">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>34.249749</v>
-      </c>
-      <c r="C11" t="str">
-        <v>134.009329</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Ｐｅｔｉｔ-Ｐｅｔｉｔｅ</v>
-      </c>
-      <c r="E11" t="str">
-        <v>761-1404 高松市香南町横井98-13</v>
-      </c>
-      <c r="F11" t="str">
-        <v>087-805-5451</v>
-      </c>
-      <c r="G11" t="str">
-        <v>宮本　尚枝</v>
-      </c>
-      <c r="H11" t="str">
-        <v>H27.8.1</v>
-      </c>
-      <c r="I11" t="str">
-        <v>8：00～18：00（18：00～8：00）</v>
-      </c>
-      <c r="J11" t="str">
-        <v>8：00～18：00（18：00～8：00）</v>
-      </c>
-      <c r="K11" t="str">
-        <v>8：00～18：00（18：00～8：00）</v>
-      </c>
-      <c r="L11" t="str">
-        <v>5</v>
-      </c>
-      <c r="M11" t="str">
-        <v>5ヶ月～3歳児</v>
-      </c>
-      <c r="N11" t="str">
-        <v>月極め、一時預かり、夜間保育、24時間保育</v>
-      </c>
-      <c r="O11" t="str">
-        <v>構造：木造2階建ての1階（集合住宅）、保育室：9.9㎡、屋外：なし</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>11</v>
-      </c>
-      <c r="B12" t="str">
-        <v>34.350335</v>
-      </c>
-      <c r="C12" t="str">
-        <v>134.056131</v>
-      </c>
-      <c r="D12" t="str">
-        <v>事業所内保育所たまも（休止中）</v>
-      </c>
-      <c r="E12" t="str">
-        <v>760-0031 高松市北浜町7-10</v>
-      </c>
-      <c r="F12" t="str">
-        <v>087-811-4450</v>
-      </c>
-      <c r="G12" t="str">
-        <v>社会福祉法人さぬき　理事長　藤目　真晧</v>
-      </c>
-      <c r="H12" t="str">
-        <v>H27.1.5</v>
-      </c>
-      <c r="I12" t="str">
-        <v>ー</v>
-      </c>
-      <c r="J12" t="str">
-        <v>ー</v>
-      </c>
-      <c r="K12" t="str">
-        <v>ー</v>
-      </c>
-      <c r="L12" t="str">
-        <v>ー</v>
-      </c>
       <c r="M12" t="str">
-        <v>3ヶ月～5歳児</v>
+        <v>0～2歳児</v>
       </c>
       <c r="N12" t="str">
         <v>月極め、一時預かり</v>
       </c>
       <c r="O12" t="str">
-        <v>構造：鉄筋コンクリート造6階建ての1階（老人福祉施設）、保育室：95.00㎡、屋外：なし</v>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
+        <v>構造：鉄骨造2階建ての１階（専用建物）、保育室：29.6㎡、屋外：なし</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="str">
-        <v>34.292238</v>
+        <v>34.32573</v>
       </c>
       <c r="C13" t="str">
-        <v>134.029099</v>
+        <v>134.061684</v>
       </c>
       <c r="D13" t="str">
-        <v>託児所 エンジェル</v>
+        <v>英語保育園　リトル　ダビンチ</v>
       </c>
       <c r="E13" t="str">
-        <v>761-8084 高松市一宮町880番地1</v>
+        <v>760-0078 高松市今里町二丁目4-10</v>
       </c>
       <c r="F13" t="str">
-        <v>087-814-3575</v>
+        <v>087-813-6378</v>
       </c>
       <c r="G13" t="str">
-        <v>社会福祉法人　喜勝会　理事長　小出　克元</v>
+        <v>株式会社　englishbiz　代表取締役　グルネウォルド　マーク　エイドリアン</v>
       </c>
       <c r="H13" t="str">
-        <v>H24.11.1</v>
+        <v>H29.4.10</v>
       </c>
       <c r="I13" t="str">
-        <v>8：30～17：30（7：30～8：30,17：30～18：30）</v>
+        <v>9：00～14：00</v>
       </c>
       <c r="J13" t="str">
-        <v>8：30～17：30（7：30～8：30,17：30～18：30）</v>
-      </c>
-      <c r="K13" t="str" xml:space="preserve">
-        <v xml:space="preserve">祝：8：30～17：30（7：30～8：30,17：30～18：30）
-日：休</v>
+        <v>休</v>
+      </c>
+      <c r="K13" t="str">
+        <v>休</v>
       </c>
       <c r="L13" t="str">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M13" t="str">
-        <v>0～2歳児</v>
+        <v>2～5歳児</v>
       </c>
       <c r="N13" t="str">
-        <v>月極め、一時預かり</v>
+        <v>月極め</v>
       </c>
       <c r="O13" t="str">
-        <v>構造：鉄骨造2階建ての１階（専用建物）、保育室：29.6㎡、屋外：なし</v>
+        <v>構造：鉄筋コンクリート造2階建ての2階（事務所用建物）、保育室：28.98㎡、屋外：なし</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="str">
-        <v>34.32573</v>
+        <v>34.343479</v>
       </c>
       <c r="C14" t="str">
-        <v>134.061684</v>
+        <v>134.044132</v>
       </c>
       <c r="D14" t="str">
-        <v>英語保育園　リトル　ダビンチ</v>
+        <v>高松インターナショナルスクール</v>
       </c>
       <c r="E14" t="str">
-        <v>760-0078 高松市今里町二丁目4-10</v>
+        <v>760-0017 高松市番町2-4-2７　番町スクエア２F</v>
       </c>
       <c r="F14" t="str">
-        <v>087-813-6378</v>
+        <v>087-813-3138</v>
       </c>
       <c r="G14" t="str">
-        <v>株式会社　englishbiz　代表取締役　グルネウォルド　マーク　エイドリアン</v>
+        <v>ACKRY株式会社　代表取締役　山口　明裕</v>
       </c>
       <c r="H14" t="str">
-        <v>H29.4.10</v>
+        <v>H30.4.1</v>
       </c>
       <c r="I14" t="str">
-        <v>9：00～14：00</v>
+        <v>9：00～17：00（8：00～9：00,17：00～18：00）</v>
       </c>
       <c r="J14" t="str">
-        <v>休</v>
+        <v>10：00～13：00（8：00～10：00）</v>
       </c>
       <c r="K14" t="str">
         <v>休</v>
@@ -1049,45 +1049,45 @@
         <v>15</v>
       </c>
       <c r="M14" t="str">
-        <v>2～5歳児</v>
+        <v>1～5歳児</v>
       </c>
       <c r="N14" t="str">
-        <v>月極め</v>
+        <v>月極め、春/冬/春休み短期プログラム</v>
       </c>
       <c r="O14" t="str">
-        <v>構造：鉄筋コンクリート造2階建ての2階（事務所用建物）、保育室：28.98㎡、屋外：なし</v>
+        <v>構造：鉄筋コンクリート5階建ての2階（事務所用建物）、保育室：72.85㎡、屋外：なし</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="str">
-        <v>34.343479</v>
+        <v>34.22806</v>
       </c>
       <c r="C15" t="str">
-        <v>134.044132</v>
+        <v>134.078483</v>
       </c>
       <c r="D15" t="str">
-        <v>高松インターナショナルスクール</v>
+        <v>森のようちえんお山歩隊</v>
       </c>
       <c r="E15" t="str">
-        <v>760-0017 高松市番町2-4-2７　番町スクエア２F</v>
+        <v>761-0445 高松市西植田町6047</v>
       </c>
       <c r="F15" t="str">
-        <v>087-813-3138</v>
+        <v>090-2820-3076</v>
       </c>
       <c r="G15" t="str">
-        <v>ACKRY株式会社　代表取締役　山口　明裕</v>
+        <v>特定非営利活動法人　森のようちえんお山歩隊　代表理事　湊　千恵</v>
       </c>
       <c r="H15" t="str">
-        <v>H30.4.1</v>
+        <v>H31.4.1</v>
       </c>
       <c r="I15" t="str">
-        <v>9：00～17：00（8：00～9：00,17：00～18：00）</v>
+        <v>9：15～14：15</v>
       </c>
       <c r="J15" t="str">
-        <v>10：00～13：00（8：00～10：00）</v>
+        <v>休</v>
       </c>
       <c r="K15" t="str">
         <v>休</v>
@@ -1096,42 +1096,42 @@
         <v>15</v>
       </c>
       <c r="M15" t="str">
-        <v>1～5歳児</v>
+        <v>3歳児～就学前</v>
       </c>
       <c r="N15" t="str">
-        <v>月極め、春/冬/春休み短期プログラム</v>
+        <v>月極め</v>
       </c>
       <c r="O15" t="str">
-        <v>構造：鉄筋コンクリート5階建ての2階（事務所用建物）、保育室：72.85㎡、屋外：なし</v>
+        <v>構造：木造1階建て（専用建物）、保育室：27.75㎡、屋外：133.73㎡</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="str">
-        <v>34.22806</v>
+        <v>34.3434094</v>
       </c>
       <c r="C16" t="str">
-        <v>134.078483</v>
+        <v>134.032015</v>
       </c>
       <c r="D16" t="str">
-        <v>森のようちえんお山歩隊</v>
+        <v>二番丁幼稚園</v>
       </c>
       <c r="E16" t="str">
-        <v>761-0445 高松市西植田町6047</v>
+        <v>760-0014 高松市昭和町二丁目7-1</v>
       </c>
       <c r="F16" t="str">
-        <v>090-2820-3076</v>
+        <v>087-861-3575</v>
       </c>
       <c r="G16" t="str">
-        <v>特定非営利活動法人　森のようちえんお山歩隊　代表理事　湊　千恵</v>
+        <v>学校法人　二番丁学園　理事長　栗　秀代</v>
       </c>
       <c r="H16" t="str">
-        <v>H31.4.1</v>
+        <v>H30.4.1</v>
       </c>
       <c r="I16" t="str">
-        <v>9：15～14：15</v>
+        <v>7：30～14：30（14：30～19：30）</v>
       </c>
       <c r="J16" t="str">
         <v>休</v>
@@ -1140,45 +1140,45 @@
         <v>休</v>
       </c>
       <c r="L16" t="str">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M16" t="str">
-        <v>3歳児～就学前</v>
+        <v>2歳児</v>
       </c>
       <c r="N16" t="str">
-        <v>月極め</v>
+        <v>月極め、一時預かり</v>
       </c>
       <c r="O16" t="str">
-        <v>構造：木造1階建て（専用建物）、保育室：27.75㎡、屋外：133.73㎡</v>
+        <v>構造：鉄骨造・鉄筋コンクリート造2階建ての1階（専用建物）、保育室：329.04㎡、屋外：732.85㎡</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="str">
-        <v>34.3434094</v>
+        <v>34.347514</v>
       </c>
       <c r="C17" t="str">
-        <v>134.032015</v>
+        <v>134.058265</v>
       </c>
       <c r="D17" t="str">
-        <v>二番丁幼稚園</v>
+        <v>香川県立中央病院附属保育所</v>
       </c>
       <c r="E17" t="str">
-        <v>760-0014 高松市昭和町二丁目7-1</v>
+        <v>760-8557 高松市朝日町一丁目2番1号</v>
       </c>
       <c r="F17" t="str">
-        <v>087-861-3575</v>
+        <v>087-811-3333</v>
       </c>
       <c r="G17" t="str">
-        <v>学校法人　二番丁学園　理事長　栗　秀代</v>
+        <v>香川県立中央病院　院長　高口　浩一</v>
       </c>
       <c r="H17" t="str">
-        <v>H30.4.1</v>
+        <v>S49.9.2</v>
       </c>
       <c r="I17" t="str">
-        <v>7：30～14：30（14：30～19：30）</v>
+        <v>7：30～19：30（月水19：30～7：30,火木金19：30～20：30）</v>
       </c>
       <c r="J17" t="str">
         <v>休</v>
@@ -1187,45 +1187,45 @@
         <v>休</v>
       </c>
       <c r="L17" t="str">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="M17" t="str">
-        <v>2歳児</v>
+        <v>0.3～3歳児</v>
       </c>
       <c r="N17" t="str">
-        <v>月極め、一時預かり</v>
+        <v>月極め、一時預かり、夜間保育</v>
       </c>
       <c r="O17" t="str">
-        <v>構造：鉄骨造・鉄筋コンクリート造2階建ての1階（専用建物）、保育室：329.04㎡、屋外：732.85㎡</v>
+        <v>構造：木造1階建て（専用建物）、保育室：27.75㎡、屋外：133.73㎡135.90㎡屋外：あり</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="str">
-        <v>34.347514</v>
+        <v>34.345955</v>
       </c>
       <c r="C18" t="str">
-        <v>134.058265</v>
+        <v>134.088467</v>
       </c>
       <c r="D18" t="str">
-        <v>香川県立中央病院附属保育所</v>
+        <v>屋島総合病院院内保育所</v>
       </c>
       <c r="E18" t="str">
-        <v>760-8557 高松市朝日町一丁目2番1号</v>
+        <v>761-0186 高松市屋島西町2105番17</v>
       </c>
       <c r="F18" t="str">
-        <v>087-811-3333</v>
+        <v>087-841-9141</v>
       </c>
       <c r="G18" t="str">
-        <v>香川県立中央病院　院長　高口　浩一</v>
+        <v>香川県厚生農業協同組合連合会　代表理事理事長　田宮　隆</v>
       </c>
       <c r="H18" t="str">
-        <v>S49.9.2</v>
+        <v>S40.4.1</v>
       </c>
       <c r="I18" t="str">
-        <v>7：30～19：30（月水19：30～7：30,火木金19：30～20：30）</v>
+        <v>8：00～17：00（7：30～8：30,17：00～20：00）</v>
       </c>
       <c r="J18" t="str">
         <v>休</v>
@@ -1234,461 +1234,461 @@
         <v>休</v>
       </c>
       <c r="L18" t="str">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M18" t="str">
-        <v>0.3～3歳児</v>
+        <v>0～3歳児</v>
       </c>
       <c r="N18" t="str">
-        <v>月極め、一時預かり、夜間保育</v>
+        <v>月極め、一時預かり</v>
       </c>
       <c r="O18" t="str">
-        <v>構造：木造1階建て（専用建物）、保育室：27.75㎡、屋外：133.73㎡135.90㎡屋外：あり</v>
+        <v>構造：鉄筋コンクリート造4階建ての2階（病院建物）、保育室：188.6㎡、屋外：264㎡</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="str">
-        <v>34.345955</v>
+        <v>34.340639</v>
       </c>
       <c r="C19" t="str">
-        <v>134.088467</v>
+        <v>134.041318</v>
       </c>
       <c r="D19" t="str">
-        <v>屋島総合病院院内保育所</v>
+        <v>高松赤十字病院院内保育所</v>
       </c>
       <c r="E19" t="str">
-        <v>761-0186 高松市屋島西町2105番17</v>
+        <v>760-0017 高松市番町四丁目14番20号</v>
       </c>
       <c r="F19" t="str">
-        <v>087-841-9141</v>
+        <v>087-813-2056</v>
       </c>
       <c r="G19" t="str">
-        <v>香川県厚生農業協同組合連合会　代表理事理事長　田宮　隆</v>
+        <v>高松赤十字病院　院長　西村　健夫</v>
       </c>
       <c r="H19" t="str">
-        <v>S40.4.1</v>
+        <v>H15.11.1</v>
       </c>
       <c r="I19" t="str">
-        <v>8：00～17：00（7：30～8：30,17：00～20：00）</v>
+        <v>7：30～18：10（18：10～19：45）</v>
       </c>
       <c r="J19" t="str">
-        <v>休</v>
+        <v>7：30～18：10（18：10～19：00）</v>
       </c>
       <c r="K19" t="str">
         <v>休</v>
       </c>
       <c r="L19" t="str">
+        <v>40</v>
+      </c>
+      <c r="M19" t="str">
+        <v>3～4ヶ月～2歳児</v>
+      </c>
+      <c r="N19" t="str">
+        <v>月極め、夜間保育、体調不良時保育</v>
+      </c>
+      <c r="O19" t="str">
+        <v>構造：鉄骨造5階建ての1階（事務所用建物）、保育室：188.6㎡、屋外：264㎡</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
         <v>20</v>
       </c>
-      <c r="M19" t="str">
-        <v>0～3歳児</v>
-      </c>
-      <c r="N19" t="str">
-        <v>月極め、一時預かり</v>
-      </c>
-      <c r="O19" t="str">
-        <v>構造：鉄筋コンクリート造4階建ての2階（病院建物）、保育室：188.6㎡、屋外：264㎡</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>19</v>
-      </c>
       <c r="B20" t="str">
-        <v>34.340639</v>
+        <v>34.333166</v>
       </c>
       <c r="C20" t="str">
-        <v>134.041318</v>
+        <v>134.002993</v>
       </c>
       <c r="D20" t="str">
-        <v>高松赤十字病院院内保育所</v>
+        <v>キナシ大林病院すみれ保育園</v>
       </c>
       <c r="E20" t="str">
-        <v>760-0017 高松市番町四丁目14番20号</v>
+        <v>761-8014 高松市香西南町235</v>
       </c>
       <c r="F20" t="str">
-        <v>087-813-2056</v>
+        <v>087-881-6250</v>
       </c>
       <c r="G20" t="str">
-        <v>高松赤十字病院　院長　西村　健夫</v>
+        <v>医療法人財団　博仁会　キナシ大林病院　理事長　川上　由佳</v>
       </c>
       <c r="H20" t="str">
-        <v>H15.11.1</v>
-      </c>
-      <c r="I20" t="str">
-        <v>7：30～18：10（18：10～19：45）</v>
-      </c>
-      <c r="J20" t="str">
-        <v>7：30～18：10（18：10～19：00）</v>
-      </c>
-      <c r="K20" t="str">
-        <v>休</v>
-      </c>
-      <c r="L20" t="str">
-        <v>40</v>
-      </c>
-      <c r="M20" t="str">
-        <v>3～4ヶ月～2歳児</v>
-      </c>
-      <c r="N20" t="str">
-        <v>月極め、夜間保育、体調不良時保育</v>
-      </c>
-      <c r="O20" t="str">
-        <v>構造：鉄骨造5階建ての1階（事務所用建物）、保育室：188.6㎡、屋外：264㎡</v>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21" t="str">
-        <v>20</v>
-      </c>
-      <c r="B21" t="str">
-        <v>34.333166</v>
-      </c>
-      <c r="C21" t="str">
-        <v>134.002993</v>
-      </c>
-      <c r="D21" t="str">
-        <v>キナシ大林病院すみれ保育園</v>
-      </c>
-      <c r="E21" t="str">
-        <v>761-8014 高松市香西南町235</v>
-      </c>
-      <c r="F21" t="str">
-        <v>087-881-6250</v>
-      </c>
-      <c r="G21" t="str">
-        <v>医療法人財団　博仁会　キナシ大林病院　理事長　川上　由佳</v>
-      </c>
-      <c r="H21" t="str">
         <v>H2.12.1</v>
       </c>
-      <c r="I21" t="str" xml:space="preserve">
+      <c r="I20" t="str" xml:space="preserve">
         <v xml:space="preserve">月火木金　8：00～18：00
 第１・３・５水　8：00～13：00
 第2・4水　8：00～18：00</v>
       </c>
+      <c r="J20" t="str">
+        <v>8：00～18：00</v>
+      </c>
+      <c r="K20" t="str">
+        <v>休</v>
+      </c>
+      <c r="L20" t="str">
+        <v>20</v>
+      </c>
+      <c r="M20" t="str">
+        <v>2ヶ月～3歳児</v>
+      </c>
+      <c r="N20" t="str">
+        <v>月極め、一時預かり</v>
+      </c>
+      <c r="O20" t="str">
+        <v>構造：木造1階建て（専用建物）、保育室：81.0㎡、屋外：200㎡</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>21</v>
+      </c>
+      <c r="B21" t="str">
+        <v>34.296151</v>
+      </c>
+      <c r="C21" t="str">
+        <v>134.057728</v>
+      </c>
+      <c r="D21" t="str">
+        <v>香川県済生会病院なでしこ保育所</v>
+      </c>
+      <c r="E21" t="str">
+        <v>761-8076 高松市多肥上町1296番地5</v>
+      </c>
+      <c r="F21" t="str">
+        <v>087-802-7718</v>
+      </c>
+      <c r="G21" t="str">
+        <v>社会福祉法人　恩賜財団　済生会支部　香川県済生会　支部長　一井　眞比古</v>
+      </c>
+      <c r="H21" t="str">
+        <v>H2.4.1</v>
+      </c>
+      <c r="I21" t="str">
+        <v>8：00～18：00（18：00～20：00）</v>
+      </c>
       <c r="J21" t="str">
-        <v>8：00～18：00</v>
+        <v>8：00～18：00（18：00～20：00）</v>
       </c>
       <c r="K21" t="str">
         <v>休</v>
       </c>
       <c r="L21" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M21" t="str">
-        <v>2ヶ月～3歳児</v>
+        <v>0～5歳児</v>
       </c>
       <c r="N21" t="str">
-        <v>月極め、一時預かり</v>
+        <v>月極め、一時預かり、24時間保育</v>
       </c>
       <c r="O21" t="str">
-        <v>構造：木造1階建て（専用建物）、保育室：81.0㎡、屋外：200㎡</v>
+        <v>構造：鉄骨造2階建ての1階（業務用建物）、保育室：161.50㎡、屋外：72.94㎡</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="str">
-        <v>34.296151</v>
+        <v>34.235767</v>
       </c>
       <c r="C22" t="str">
-        <v>134.057728</v>
+        <v>134.020248</v>
       </c>
       <c r="D22" t="str">
-        <v>香川県済生会病院なでしこ保育所</v>
+        <v>いわき託児所</v>
       </c>
       <c r="E22" t="str">
-        <v>761-8076 高松市多肥上町1296番地5</v>
+        <v>761-1402 高松市香南町由佐13-6</v>
       </c>
       <c r="F22" t="str">
-        <v>087-802-7718</v>
+        <v>087-879-3013</v>
       </c>
       <c r="G22" t="str">
-        <v>社会福祉法人　恩賜財団　済生会支部　香川県済生会　支部長　一井　眞比古</v>
+        <v>医療法人社団　以和貴会　理事長　渡邊　朋之</v>
       </c>
       <c r="H22" t="str">
-        <v>H2.4.1</v>
+        <v>H10.10.1</v>
       </c>
       <c r="I22" t="str">
-        <v>8：00～18：00（18：00～20：00）</v>
+        <v>ー</v>
       </c>
       <c r="J22" t="str">
-        <v>8：00～18：00（18：00～20：00）</v>
+        <v>ー</v>
       </c>
       <c r="K22" t="str">
-        <v>休</v>
+        <v>ー</v>
       </c>
       <c r="L22" t="str">
-        <v>30</v>
+        <v>ー</v>
       </c>
       <c r="M22" t="str">
-        <v>0～5歳児</v>
+        <v>3ヶ月～5歳児</v>
       </c>
       <c r="N22" t="str">
-        <v>月極め、一時預かり、24時間保育</v>
+        <v>月極め、一時預かり</v>
       </c>
       <c r="O22" t="str">
-        <v>構造：鉄骨造2階建ての1階（業務用建物）、保育室：161.50㎡、屋外：72.94㎡</v>
+        <v>構造：木造2階建ての1階（専用建物）、保育室：51.93㎡、屋外：なし</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="str">
-        <v>34.235767</v>
+        <v>34.307365</v>
       </c>
       <c r="C23" t="str">
-        <v>134.020248</v>
+        <v>134.031306</v>
       </c>
       <c r="D23" t="str">
-        <v>いわき託児所</v>
+        <v>社会福祉法人　かがわ総合リハビリテーション事業団　付属保育施設　さくら保育園</v>
       </c>
       <c r="E23" t="str">
-        <v>761-1402 高松市香南町由佐13-6</v>
+        <v>761-8057 高松市田村町1114</v>
       </c>
       <c r="F23" t="str">
-        <v>087-879-3013</v>
+        <v>087-867-6008</v>
       </c>
       <c r="G23" t="str">
-        <v>医療法人社団　以和貴会　理事長　渡邊　朋之</v>
+        <v>社会福祉法人　かがわ総合リハビリテーション事業団　理事長　松尾　恭成</v>
       </c>
       <c r="H23" t="str">
-        <v>H10.10.1</v>
+        <v>H21.4.1</v>
       </c>
       <c r="I23" t="str">
-        <v>ー</v>
+        <v>8：00～18：00（18：00～8：00）</v>
       </c>
       <c r="J23" t="str">
-        <v>ー</v>
+        <v>8：00～18：00利用児がいるときのみ開所</v>
       </c>
       <c r="K23" t="str">
-        <v>ー</v>
+        <v>8：00～18：00</v>
       </c>
       <c r="L23" t="str">
-        <v>ー</v>
+        <v>15</v>
       </c>
       <c r="M23" t="str">
-        <v>3ヶ月～5歳児</v>
+        <v>生後100日～5歳児</v>
       </c>
       <c r="N23" t="str">
-        <v>月極め、一時預かり</v>
+        <v>月極め、一時預かり、24時間保育</v>
       </c>
       <c r="O23" t="str">
-        <v>構造：木造2階建ての1階（専用建物）、保育室：51.93㎡、屋外：なし</v>
+        <v>構造：鉄筋コンクリート造2階建ての1階（業務用建物）、保育室：70.81㎡、屋外：あり</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="str">
-        <v>34.307365</v>
+        <v>34.328152</v>
       </c>
       <c r="C24" t="str">
-        <v>134.031306</v>
+        <v>134.049889</v>
       </c>
       <c r="D24" t="str">
-        <v>社会福祉法人　かがわ総合リハビリテーション事業団　付属保育施設　さくら保育園</v>
+        <v>りつりん病院りつりん保育所</v>
       </c>
       <c r="E24" t="str">
-        <v>761-8057 高松市田村町1114</v>
+        <v>760-0073 高松市栗林町3-8-3</v>
       </c>
       <c r="F24" t="str">
-        <v>087-867-6008</v>
+        <v>087-802-1190</v>
       </c>
       <c r="G24" t="str">
-        <v>社会福祉法人　かがわ総合リハビリテーション事業団　理事長　松尾　恭成</v>
+        <v>独立行政法人　地域医療機能推進機構　りつりん病院　院長　大森　浩二</v>
       </c>
       <c r="H24" t="str">
-        <v>H21.4.1</v>
+        <v>H24.10.1</v>
       </c>
       <c r="I24" t="str">
-        <v>8：00～18：00（18：00～8：00）</v>
+        <v>7：30～18：00（18：00～19：00）</v>
       </c>
       <c r="J24" t="str">
-        <v>8：00～18：00利用児がいるときのみ開所</v>
+        <v>7：30～18：00（18：00～19：00）</v>
       </c>
       <c r="K24" t="str">
-        <v>8：00～18：00</v>
+        <v>休</v>
       </c>
       <c r="L24" t="str">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M24" t="str">
-        <v>生後100日～5歳児</v>
+        <v>生後57日～5歳児</v>
       </c>
       <c r="N24" t="str">
-        <v>月極め、一時預かり、24時間保育</v>
+        <v>月極め、一時預かり、夜間保育</v>
       </c>
       <c r="O24" t="str">
-        <v>構造：鉄筋コンクリート造2階建ての1階（業務用建物）、保育室：70.81㎡、屋外：あり</v>
+        <v>構造：鉄筋コンクリート造2階建ての2階（専用建物）、保育室：62.16㎡、屋外：なし</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="str">
-        <v>34.328152</v>
+        <v>34.282527</v>
       </c>
       <c r="C25" t="str">
-        <v>134.049889</v>
+        <v>134.039249</v>
       </c>
       <c r="D25" t="str">
-        <v>りつりん病院りつりん保育所</v>
+        <v>高松市立みんなの病院院内保育所「どんぐり」</v>
       </c>
       <c r="E25" t="str">
-        <v>760-0073 高松市栗林町3-8-3</v>
+        <v>761-8078 高松市仏生山町甲906番地6</v>
       </c>
       <c r="F25" t="str">
-        <v>087-802-1190</v>
+        <v>087-888-6113</v>
       </c>
       <c r="G25" t="str">
-        <v>独立行政法人　地域医療機能推進機構　りつりん病院　院長　大森　浩二</v>
+        <v>高松市病院事業管理者　和田　大助</v>
       </c>
       <c r="H25" t="str">
-        <v>H24.10.1</v>
+        <v>H30.9.1</v>
       </c>
       <c r="I25" t="str">
         <v>7：30～18：00（18：00～19：00）</v>
       </c>
       <c r="J25" t="str">
-        <v>7：30～18：00（18：00～19：00）</v>
+        <v>休</v>
       </c>
       <c r="K25" t="str">
         <v>休</v>
       </c>
       <c r="L25" t="str">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M25" t="str">
-        <v>生後57日～5歳児</v>
+        <v>2ヶ月～2歳児</v>
       </c>
       <c r="N25" t="str">
-        <v>月極め、一時預かり、夜間保育</v>
+        <v>月極め、一時預かり</v>
       </c>
       <c r="O25" t="str">
-        <v>構造：鉄筋コンクリート造2階建ての2階（専用建物）、保育室：62.16㎡、屋外：なし</v>
+        <v>構造：木造1階建て（専用建物）、保育室：86.86㎡、屋外：640.01㎡</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="str">
-        <v>34.282527</v>
+        <v>34.31959</v>
       </c>
       <c r="C26" t="str">
-        <v>134.039249</v>
+        <v>134.110738</v>
       </c>
       <c r="D26" t="str">
-        <v>高松市立みんなの病院院内保育所「どんぐり」</v>
+        <v>独立行政法人国立病院機構高松医療センターさくら保育所</v>
       </c>
       <c r="E26" t="str">
-        <v>761-8078 高松市仏生山町甲906番地6</v>
+        <v>761-0103 高松市新田町乙8番地</v>
       </c>
       <c r="F26" t="str">
-        <v>087-888-6113</v>
+        <v>087-818-0608</v>
       </c>
       <c r="G26" t="str">
-        <v>高松市病院事業管理者　和田　大助</v>
+        <v>独立行政法人　国立病院機構　高松医療センター　院長　細川　等</v>
       </c>
       <c r="H26" t="str">
-        <v>H30.9.1</v>
+        <v>S50.4.1</v>
       </c>
       <c r="I26" t="str">
-        <v>7：30～18：00（18：00～19：00）</v>
+        <v>7：30～18：30（18：30～7：30）</v>
       </c>
       <c r="J26" t="str">
-        <v>休</v>
+        <v>7：30～18：30（18：30～7：30）</v>
       </c>
       <c r="K26" t="str">
-        <v>休</v>
+        <v>7：30～18：30（18：30～7：30）</v>
       </c>
       <c r="L26" t="str">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M26" t="str">
-        <v>2ヶ月～2歳児</v>
+        <v>0.2ヶ月～5歳児</v>
       </c>
       <c r="N26" t="str">
-        <v>月極め、一時預かり</v>
+        <v>月極め、一時預かり、夜間保育、24時間保育</v>
       </c>
       <c r="O26" t="str">
-        <v>構造：木造1階建て（専用建物）、保育室：86.86㎡、屋外：640.01㎡</v>
+        <v>構造：鉄骨造1階建て（専用建物）、保育室：47.8㎡、屋外：424.06㎡</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="str">
-        <v>34.31959</v>
+        <v>34.301827</v>
       </c>
       <c r="C27" t="str">
-        <v>134.110738</v>
+        <v>134.074024</v>
       </c>
       <c r="D27" t="str">
-        <v>独立行政法人国立病院機構高松医療センターさくら保育所</v>
+        <v>香川ヤクルト販売㈱　中央保育所</v>
       </c>
       <c r="E27" t="str">
-        <v>761-0103 高松市新田町乙8番地</v>
+        <v>761-0301 高松市林町1479-1</v>
       </c>
       <c r="F27" t="str">
-        <v>087-818-0608</v>
+        <v>087-869-8960</v>
       </c>
       <c r="G27" t="str">
-        <v>独立行政法人　国立病院機構　高松医療センター　院長　細川　等</v>
+        <v>香川ヤクルト販売株式会社　代表取締役社長　町田　繁</v>
       </c>
       <c r="H27" t="str">
-        <v>S50.4.1</v>
+        <v>H20.2.1</v>
       </c>
       <c r="I27" t="str">
-        <v>7：30～18：30（18：30～7：30）</v>
+        <v>8：15～15：30</v>
       </c>
       <c r="J27" t="str">
-        <v>7：30～18：30（18：30～7：30）</v>
+        <v>休</v>
       </c>
       <c r="K27" t="str">
-        <v>7：30～18：30（18：30～7：30）</v>
+        <v>休</v>
       </c>
       <c r="L27" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M27" t="str">
-        <v>0.2ヶ月～5歳児</v>
+        <v>1～3歳児</v>
       </c>
       <c r="N27" t="str">
-        <v>月極め、一時預かり、夜間保育、24時間保育</v>
+        <v>月極め、一時預かり</v>
       </c>
       <c r="O27" t="str">
-        <v>構造：鉄骨造1階建て（専用建物）、保育室：47.8㎡、屋外：424.06㎡</v>
+        <v>構造：鉄骨造2階建ての2階（事務所用建物）、保育室：79.7㎡、屋外：なし</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" t="str">
-        <v>34.301827</v>
+        <v>34.27964</v>
       </c>
       <c r="C28" t="str">
-        <v>134.074024</v>
+        <v>134.026954</v>
       </c>
       <c r="D28" t="str">
-        <v>香川ヤクルト販売㈱　中央保育所</v>
+        <v>香川ヤクルト販売㈱　一宮保育所</v>
       </c>
       <c r="E28" t="str">
-        <v>761-0301 高松市林町1479-1</v>
+        <v>761-8085 高松市寺井町1102-1</v>
       </c>
       <c r="F28" t="str">
-        <v>087-869-8960</v>
+        <v>087-886-8917</v>
       </c>
       <c r="G28" t="str">
         <v>香川ヤクルト販売株式会社　代表取締役社長　町田　繁</v>
@@ -1715,27 +1715,27 @@
         <v>月極め、一時預かり</v>
       </c>
       <c r="O28" t="str">
-        <v>構造：鉄骨造2階建ての2階（事務所用建物）、保育室：79.7㎡、屋外：なし</v>
+        <v>構造：鉄骨造2階建ての2階（事務所用建物）、保育室：96.05㎡、屋外：なし</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" t="str">
-        <v>34.27964</v>
+        <v>34.337104</v>
       </c>
       <c r="C29" t="str">
-        <v>134.026954</v>
+        <v>134.154801</v>
       </c>
       <c r="D29" t="str">
-        <v>香川ヤクルト販売㈱　一宮保育所</v>
+        <v>香川ヤクルト販売㈱　牟礼保育所</v>
       </c>
       <c r="E29" t="str">
-        <v>761-8085 高松市寺井町1102-1</v>
+        <v>761-0122 高松市牟礼町大町1012-1</v>
       </c>
       <c r="F29" t="str">
-        <v>087-886-8917</v>
+        <v>087-845-6521</v>
       </c>
       <c r="G29" t="str">
         <v>香川ヤクルト販売株式会社　代表取締役社長　町田　繁</v>
@@ -1762,247 +1762,200 @@
         <v>月極め、一時預かり</v>
       </c>
       <c r="O29" t="str">
-        <v>構造：鉄骨造2階建ての2階（事務所用建物）、保育室：96.05㎡、屋外：なし</v>
+        <v>構造：鉄骨造1階建て（事務所用建物）、保育室：49.5㎡、屋外：なし</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" t="str">
-        <v>34.337104</v>
+        <v>34.291972</v>
       </c>
       <c r="C30" t="str">
-        <v>134.154801</v>
+        <v>133.957808</v>
       </c>
       <c r="D30" t="str">
-        <v>香川ヤクルト販売㈱　牟礼保育所</v>
+        <v>モン　シュシュ</v>
       </c>
       <c r="E30" t="str">
-        <v>761-0122 高松市牟礼町大町1012-1</v>
+        <v>769-0104 高松市国分寺町新名482-1</v>
       </c>
       <c r="F30" t="str">
-        <v>087-845-6521</v>
+        <v>087-864-9515</v>
       </c>
       <c r="G30" t="str">
-        <v>香川ヤクルト販売株式会社　代表取締役社長　町田　繁</v>
+        <v>社会福祉法人　柊会　理事長　高畠　敏史</v>
       </c>
       <c r="H30" t="str">
-        <v>H20.2.1</v>
+        <v>H27.4.1</v>
       </c>
       <c r="I30" t="str">
-        <v>8：15～15：30</v>
+        <v>8：15～18：00</v>
       </c>
       <c r="J30" t="str">
-        <v>休</v>
+        <v>8：15～18：00</v>
       </c>
       <c r="K30" t="str">
-        <v>休</v>
+        <v>8：15～18：00</v>
       </c>
       <c r="L30" t="str">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M30" t="str">
-        <v>1～3歳児</v>
+        <v>6ヶ月～5歳児</v>
       </c>
       <c r="N30" t="str">
-        <v>月極め、一時預かり</v>
+        <v>月極め</v>
       </c>
       <c r="O30" t="str">
-        <v>構造：鉄骨造1階建て（事務所用建物）、保育室：49.5㎡、屋外：なし</v>
+        <v>構造：鉄骨造3階建ての1階（業務用建物）、保育室：86.25㎡、屋外：なし</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="str">
-        <v>34.291972</v>
+        <v>34.342213</v>
       </c>
       <c r="C31" t="str">
-        <v>133.957808</v>
+        <v>134.069237</v>
       </c>
       <c r="D31" t="str">
-        <v>モン　シュシュ</v>
+        <v>あおぞら園（休止中）</v>
       </c>
       <c r="E31" t="str">
-        <v>769-0104 高松市国分寺町新名482-1</v>
+        <v>760-0066 高松市福岡町四丁目12-18</v>
       </c>
       <c r="F31" t="str">
-        <v>087-864-9515</v>
+        <v>087-880-7979</v>
       </c>
       <c r="G31" t="str">
-        <v>社会福祉法人　柊会　理事長　高畠　敏史</v>
+        <v>四国産業株式会社　代表取締役社長　鈴木　正人</v>
       </c>
       <c r="H31" t="str">
-        <v>H27.4.1</v>
+        <v>R4.6.1</v>
       </c>
       <c r="I31" t="str">
-        <v>8：15～18：00</v>
+        <v>8：45～16：45</v>
       </c>
       <c r="J31" t="str">
-        <v>8：15～18：00</v>
+        <v>休</v>
       </c>
       <c r="K31" t="str">
-        <v>8：15～18：00</v>
+        <v>休</v>
       </c>
       <c r="L31" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M31" t="str">
         <v>6ヶ月～5歳児</v>
       </c>
       <c r="N31" t="str">
-        <v>月極め</v>
+        <v>月極め、一時預かり</v>
       </c>
       <c r="O31" t="str">
-        <v>構造：鉄骨造3階建ての1階（業務用建物）、保育室：86.25㎡、屋外：なし</v>
+        <v>構造：木造2階建ての1階（専用建物）、保育室：19.8㎡、屋外：なし</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" t="str">
-        <v>34.342213</v>
+        <v>34.306063</v>
       </c>
       <c r="C32" t="str">
-        <v>134.069237</v>
+        <v>134.069463</v>
       </c>
       <c r="D32" t="str">
-        <v>あおぞら園（休止中）</v>
+        <v>日本エネルギー総合システム託児所</v>
       </c>
       <c r="E32" t="str">
-        <v>760-0066 高松市福岡町四丁目12-18</v>
+        <v>761-0301 高松市林町2536-1</v>
       </c>
       <c r="F32" t="str">
-        <v>087-880-7979</v>
+        <v>087-813-5908</v>
       </c>
       <c r="G32" t="str">
-        <v>四国産業株式会社　代表取締役社長　鈴木　正人</v>
+        <v>日本エネルギー総合システム株式会社　代表取締役　黒淵　誠二</v>
       </c>
       <c r="H32" t="str">
-        <v>R4.6.1</v>
+        <v>H30.10.16</v>
       </c>
       <c r="I32" t="str">
-        <v>8：45～16：45</v>
+        <v>8：45～18：15</v>
       </c>
       <c r="J32" t="str">
-        <v>休</v>
+        <v>8：45～18：15</v>
       </c>
       <c r="K32" t="str">
-        <v>休</v>
+        <v>8：45～18：15</v>
       </c>
       <c r="L32" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M32" t="str">
-        <v>6ヶ月～5歳児</v>
+        <v>0～5歳児</v>
       </c>
       <c r="N32" t="str">
-        <v>月極め、一時預かり</v>
+        <v>月極め</v>
       </c>
       <c r="O32" t="str">
-        <v>構造：木造2階建ての1階（専用建物）、保育室：19.8㎡、屋外：なし</v>
+        <v>構造：鉄骨造1階建て（事務所用建物）、保育室：51.77㎡、屋外：なし</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" t="str">
-        <v>34.306063</v>
+        <v>34.309614</v>
       </c>
       <c r="C33" t="str">
-        <v>134.069463</v>
+        <v>134.046213</v>
       </c>
       <c r="D33" t="str">
-        <v>日本エネルギー総合システム託児所</v>
+        <v>にこにこ保育教育研究センター附属保育園（休止中）</v>
       </c>
       <c r="E33" t="str">
-        <v>761-0301 高松市林町2536-1</v>
+        <v>761-8073 高松市太田下町2350-1</v>
       </c>
       <c r="F33" t="str">
-        <v>087-813-5908</v>
+        <v>087-802-5360</v>
       </c>
       <c r="G33" t="str">
-        <v>日本エネルギー総合システム株式会社　代表取締役　黒淵　誠二</v>
+        <v>株式会社チャイルドケア二四　代表取締役　梶尾　裕子</v>
       </c>
       <c r="H33" t="str">
-        <v>H30.10.16</v>
+        <v>R4.4.1</v>
       </c>
       <c r="I33" t="str">
-        <v>8：45～18：15</v>
+        <v>7：30～78：30（18：30～19：00）</v>
       </c>
       <c r="J33" t="str">
-        <v>8：45～18：15</v>
+        <v>7：30～18：30（18：30～19：00）</v>
       </c>
       <c r="K33" t="str">
-        <v>8：45～18：15</v>
+        <v>休</v>
       </c>
       <c r="L33" t="str">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="M33" t="str">
-        <v>0～5歳児</v>
+        <v>3～5歳児</v>
       </c>
       <c r="N33" t="str">
         <v>月極め</v>
       </c>
       <c r="O33" t="str">
-        <v>構造：鉄骨造1階建て（事務所用建物）、保育室：51.77㎡、屋外：なし</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
-        <v>34.309614</v>
-      </c>
-      <c r="C34" t="str">
-        <v>134.046213</v>
-      </c>
-      <c r="D34" t="str">
-        <v>にこにこ保育教育研究センター附属保育園（休止中）</v>
-      </c>
-      <c r="E34" t="str">
-        <v>761-8073 高松市太田下町2350-1</v>
-      </c>
-      <c r="F34" t="str">
-        <v>087-802-5360</v>
-      </c>
-      <c r="G34" t="str">
-        <v>株式会社チャイルドケア二四　代表取締役　梶尾　裕子</v>
-      </c>
-      <c r="H34" t="str">
-        <v>R4.4.1</v>
-      </c>
-      <c r="I34" t="str">
-        <v>7：30～78：30（18：30～19：00）</v>
-      </c>
-      <c r="J34" t="str">
-        <v>7：30～18：30（18：30～19：00）</v>
-      </c>
-      <c r="K34" t="str">
-        <v>休</v>
-      </c>
-      <c r="L34" t="str">
-        <v>60</v>
-      </c>
-      <c r="M34" t="str">
-        <v>3～5歳児</v>
-      </c>
-      <c r="N34" t="str">
-        <v>月極め</v>
-      </c>
-      <c r="O34" t="str">
         <v>構造：鉄骨造2階建ての1階（専用建物）、保育室：132.84㎡、屋外：なし</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O33"/>
   </ignoredErrors>
 </worksheet>
 </file>